--- a/artfynd/A 1520-2022 artfynd.xlsx
+++ b/artfynd/A 1520-2022 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>136484347</v>
       </c>
       <c r="B3" t="n">
-        <v>57917</v>
+        <v>57919</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>136484349</v>
       </c>
       <c r="B4" t="n">
-        <v>58665</v>
+        <v>58667</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 1520-2022 artfynd.xlsx
+++ b/artfynd/A 1520-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1026,6 +1026,112 @@
       <c r="AZ4" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136484349</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>136957321</v>
+      </c>
+      <c r="B5" t="n">
+        <v>108116</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>219933</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kattfot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Antennaria dioica</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Gaertn.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Sångbäckvallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>455445</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6927692</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Klövsjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Vigge Ulfsson, Ulf Swenson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136957321</t>
         </is>
       </c>
     </row>
@@ -1034,6 +1140,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 1520-2022 artfynd.xlsx
+++ b/artfynd/A 1520-2022 artfynd.xlsx
@@ -1034,7 +1034,7 @@
         <v>136957321</v>
       </c>
       <c r="B5" t="n">
-        <v>108116</v>
+        <v>108122</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 1520-2022 artfynd.xlsx
+++ b/artfynd/A 1520-2022 artfynd.xlsx
@@ -1034,7 +1034,7 @@
         <v>136957321</v>
       </c>
       <c r="B5" t="n">
-        <v>108122</v>
+        <v>108124</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 1520-2022 artfynd.xlsx
+++ b/artfynd/A 1520-2022 artfynd.xlsx
@@ -1034,7 +1034,7 @@
         <v>136957321</v>
       </c>
       <c r="B5" t="n">
-        <v>108124</v>
+        <v>108125</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 1520-2022 artfynd.xlsx
+++ b/artfynd/A 1520-2022 artfynd.xlsx
@@ -1034,7 +1034,7 @@
         <v>136957321</v>
       </c>
       <c r="B5" t="n">
-        <v>108125</v>
+        <v>108131</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 1520-2022 artfynd.xlsx
+++ b/artfynd/A 1520-2022 artfynd.xlsx
@@ -1034,7 +1034,7 @@
         <v>136957321</v>
       </c>
       <c r="B5" t="n">
-        <v>108131</v>
+        <v>108135</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 1520-2022 artfynd.xlsx
+++ b/artfynd/A 1520-2022 artfynd.xlsx
@@ -1034,7 +1034,7 @@
         <v>136957321</v>
       </c>
       <c r="B5" t="n">
-        <v>108135</v>
+        <v>108137</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 1520-2022 artfynd.xlsx
+++ b/artfynd/A 1520-2022 artfynd.xlsx
@@ -1034,7 +1034,7 @@
         <v>136957321</v>
       </c>
       <c r="B5" t="n">
-        <v>108137</v>
+        <v>108139</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 1520-2022 artfynd.xlsx
+++ b/artfynd/A 1520-2022 artfynd.xlsx
@@ -1034,7 +1034,7 @@
         <v>136957321</v>
       </c>
       <c r="B5" t="n">
-        <v>108139</v>
+        <v>108152</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 1520-2022 artfynd.xlsx
+++ b/artfynd/A 1520-2022 artfynd.xlsx
@@ -1034,7 +1034,7 @@
         <v>136957321</v>
       </c>
       <c r="B5" t="n">
-        <v>108152</v>
+        <v>108154</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 1520-2022 artfynd.xlsx
+++ b/artfynd/A 1520-2022 artfynd.xlsx
@@ -1034,7 +1034,7 @@
         <v>136957321</v>
       </c>
       <c r="B5" t="n">
-        <v>108154</v>
+        <v>108158</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 1520-2022 artfynd.xlsx
+++ b/artfynd/A 1520-2022 artfynd.xlsx
@@ -1034,7 +1034,7 @@
         <v>136957321</v>
       </c>
       <c r="B5" t="n">
-        <v>108158</v>
+        <v>108179</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 1520-2022 artfynd.xlsx
+++ b/artfynd/A 1520-2022 artfynd.xlsx
@@ -1034,7 +1034,7 @@
         <v>136957321</v>
       </c>
       <c r="B5" t="n">
-        <v>108179</v>
+        <v>108180</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 1520-2022 artfynd.xlsx
+++ b/artfynd/A 1520-2022 artfynd.xlsx
@@ -1034,7 +1034,7 @@
         <v>136957321</v>
       </c>
       <c r="B5" t="n">
-        <v>108180</v>
+        <v>108185</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 1520-2022 artfynd.xlsx
+++ b/artfynd/A 1520-2022 artfynd.xlsx
@@ -1034,7 +1034,7 @@
         <v>136957321</v>
       </c>
       <c r="B5" t="n">
-        <v>108185</v>
+        <v>108188</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 1520-2022 artfynd.xlsx
+++ b/artfynd/A 1520-2022 artfynd.xlsx
@@ -1034,7 +1034,7 @@
         <v>136957321</v>
       </c>
       <c r="B5" t="n">
-        <v>108188</v>
+        <v>108194</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 1520-2022 artfynd.xlsx
+++ b/artfynd/A 1520-2022 artfynd.xlsx
@@ -1034,7 +1034,7 @@
         <v>136957321</v>
       </c>
       <c r="B5" t="n">
-        <v>108194</v>
+        <v>108195</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 1520-2022 artfynd.xlsx
+++ b/artfynd/A 1520-2022 artfynd.xlsx
@@ -1034,7 +1034,7 @@
         <v>136957321</v>
       </c>
       <c r="B5" t="n">
-        <v>108195</v>
+        <v>108207</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 1520-2022 artfynd.xlsx
+++ b/artfynd/A 1520-2022 artfynd.xlsx
@@ -1034,7 +1034,7 @@
         <v>136957321</v>
       </c>
       <c r="B5" t="n">
-        <v>108207</v>
+        <v>108208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 1520-2022 artfynd.xlsx
+++ b/artfynd/A 1520-2022 artfynd.xlsx
@@ -1034,7 +1034,7 @@
         <v>136957321</v>
       </c>
       <c r="B5" t="n">
-        <v>108208</v>
+        <v>108211</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 1520-2022 artfynd.xlsx
+++ b/artfynd/A 1520-2022 artfynd.xlsx
@@ -1034,7 +1034,7 @@
         <v>136957321</v>
       </c>
       <c r="B5" t="n">
-        <v>108211</v>
+        <v>108213</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 1520-2022 artfynd.xlsx
+++ b/artfynd/A 1520-2022 artfynd.xlsx
@@ -1034,7 +1034,7 @@
         <v>136957321</v>
       </c>
       <c r="B5" t="n">
-        <v>108213</v>
+        <v>108217</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
